--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU18"/>
+  <dimension ref="A1:BV18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="30"/>
@@ -510,6 +510,7 @@
     <col customWidth="1" max="71" min="71" width="13"/>
     <col customWidth="1" max="72" min="72" width="13"/>
     <col customWidth="1" max="73" min="73" width="13"/>
+    <col customWidth="1" max="74" min="74" width="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,6 +879,11 @@
           <t>22.02 20:45</t>
         </is>
       </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>01.04 00:05</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1101,6 +1107,9 @@
       <c r="BU2" t="n">
         <v>22</v>
       </c>
+      <c r="BV2" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1324,6 +1333,9 @@
       <c r="BU3" t="n">
         <v>9</v>
       </c>
+      <c r="BV3" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1547,6 +1559,9 @@
       <c r="BU4" s="1" t="n">
         <v>33</v>
       </c>
+      <c r="BV4" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1770,6 +1785,9 @@
       <c r="BU5" t="n">
         <v>10</v>
       </c>
+      <c r="BV5" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1993,6 +2011,9 @@
       <c r="BU6" t="n">
         <v>9</v>
       </c>
+      <c r="BV6" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2216,6 +2237,9 @@
       <c r="BU7" t="n">
         <v>13</v>
       </c>
+      <c r="BV7" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2439,6 +2463,9 @@
       <c r="BU8" t="n">
         <v>3</v>
       </c>
+      <c r="BV8" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2662,6 +2689,9 @@
       <c r="BU9" t="n">
         <v>6</v>
       </c>
+      <c r="BV9" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2885,6 +2915,9 @@
       <c r="BU10" t="n">
         <v>5</v>
       </c>
+      <c r="BV10" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3108,6 +3141,9 @@
       <c r="BU11" t="n">
         <v>15</v>
       </c>
+      <c r="BV11" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3331,6 +3367,9 @@
       <c r="BU12" t="n">
         <v>14</v>
       </c>
+      <c r="BV12" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3554,6 +3593,9 @@
       <c r="BU13" t="n">
         <v>10</v>
       </c>
+      <c r="BV13" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3777,6 +3819,9 @@
       <c r="BU14" t="n">
         <v>6</v>
       </c>
+      <c r="BV14" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4000,6 +4045,9 @@
       <c r="BU15" s="1" t="n">
         <v>11</v>
       </c>
+      <c r="BV15" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4223,6 +4271,9 @@
       <c r="BU16" s="1" t="n">
         <v>22</v>
       </c>
+      <c r="BV16" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4444,6 +4495,9 @@
         <v>0</v>
       </c>
       <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4663,6 +4717,9 @@
       </c>
       <c r="BU18" s="3" t="n">
         <v>188</v>
+      </c>
+      <c r="BV18" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV18"/>
+  <dimension ref="A1:BW18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="30"/>
@@ -511,6 +511,7 @@
     <col customWidth="1" max="72" min="72" width="13"/>
     <col customWidth="1" max="73" min="73" width="13"/>
     <col customWidth="1" max="74" min="74" width="13"/>
+    <col customWidth="1" max="75" min="75" width="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -884,6 +885,11 @@
           <t>01.04 00:05</t>
         </is>
       </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>01.04 01:50</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1110,6 +1116,9 @@
       <c r="BV2" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="BW2" s="1" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1336,6 +1345,9 @@
       <c r="BV3" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="BW3" s="1" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1562,6 +1574,9 @@
       <c r="BV4" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="BW4" s="1" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1788,6 +1803,9 @@
       <c r="BV5" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="BW5" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2014,6 +2032,9 @@
       <c r="BV6" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="BW6" s="1" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2240,6 +2261,9 @@
       <c r="BV7" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="BW7" s="1" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2466,6 +2490,9 @@
       <c r="BV8" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="BW8" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2692,6 +2719,9 @@
       <c r="BV9" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="BW9" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2918,6 +2948,9 @@
       <c r="BV10" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="BW10" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3144,6 +3177,9 @@
       <c r="BV11" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="BW11" s="1" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3370,6 +3406,9 @@
       <c r="BV12" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="BW12" s="1" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3596,6 +3635,9 @@
       <c r="BV13" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="BW13" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3822,6 +3864,9 @@
       <c r="BV14" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="BW14" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4048,6 +4093,9 @@
       <c r="BV15" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="BW15" s="1" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4274,6 +4322,9 @@
       <c r="BV16" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="BW16" s="1" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4498,6 +4549,9 @@
         <v>0</v>
       </c>
       <c r="BV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4720,6 +4774,9 @@
       </c>
       <c r="BV18" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="BW18" s="3" t="n">
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D3D3D3"/>
+        <bgColor rgb="00D3D3D3"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -44,15 +50,16 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -413,10 +420,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="19"/>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -425,8 +433,358 @@
           <t>название рассказа</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>20.06 11:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Вместо сердца</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Двадцать Седьмая</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Настенька</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Три таланта лжи</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Попробуй снова</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Лжизм</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Кафедра</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Мертвецы и голуби</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dety Free</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>В сорок лет жизнь только начинается</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>А ты помнишь?</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Дело о цветах</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Регламент лжи для мёртвых</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Великий Урр</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Элегия с блинами</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Спасенная богами</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Сережки с рубинами</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Вне зоны доступа</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Кто убил Тома Харди?</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Мелиранка</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Снят с голосования</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>История одного расследования</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>В тени закона</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Второе свидание</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Первое свидание с клёвой девчонкой, земной, но немного ненастоящей</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Кирки и лопаты</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>И стал дом</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Про любовь</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Пастушок</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Самое первое свидание</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Разменная монета Гекаты</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Этот корыстный, фальшивый мир</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Чёртова погода</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Что-то будет написано на табличке?</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="1" t="n">
+        <v>210</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -420,10 +420,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -435,353 +435,73 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>20.06 11:49</t>
+          <t>06.07 16:48</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Вместо сердца</t>
+          <t>Волшебник Костя</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Двадцать Седьмая</t>
+          <t>32 мая</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Настенька</t>
+          <t>Никого не жалко, никого.</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Три таланта лжи</t>
+          <t>Три такта вальса «Достучаться до небес»</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Попробуй снова</t>
+          <t>Олежек.</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Лжизм</t>
+          <t>Я из тех, кто.</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Кафедра</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Мертвецы и голуби</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Dety Free</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>В сорок лет жизнь только начинается</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>А ты помнишь?</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Дело о цветах</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Регламент лжи для мёртвых</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Великий Урр</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Элегия с блинами</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Спасенная богами</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Сережки с рубинами</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Вне зоны доступа</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Кто убил Тома Харди?</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Мелиранка</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Снят с голосования</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>История одного расследования</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>В тени закона</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Второе свидание</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Первое свидание с клёвой девчонкой, земной, но немного ненастоящей</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Кирки и лопаты</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>И стал дом</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Про любовь</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Пастушок</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Самое первое свидание</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Разменная монета Гекаты</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Этот корыстный, фальшивый мир</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Чёртова погода</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Что-то будет написано на табличке?</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="1" t="n">
-        <v>210</v>
+      <c r="B8" s="1" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -52,9 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,11 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -438,6 +446,11 @@
           <t>06.07 16:48</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>07.07 06:25</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -448,6 +461,9 @@
       <c r="B2" t="n">
         <v>7</v>
       </c>
+      <c r="C2" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -458,6 +474,9 @@
       <c r="B3" t="n">
         <v>3</v>
       </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -468,6 +487,9 @@
       <c r="B4" t="n">
         <v>9</v>
       </c>
+      <c r="C4" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -478,6 +500,9 @@
       <c r="B5" t="n">
         <v>5</v>
       </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -488,6 +513,9 @@
       <c r="B6" t="n">
         <v>3</v>
       </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -498,10 +526,16 @@
       <c r="B7" t="n">
         <v>4</v>
       </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>31</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -427,12 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,6 +452,11 @@
           <t>07.07 06:25</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>07.07 09:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -464,6 +470,9 @@
       <c r="C2" t="n">
         <v>7</v>
       </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -477,6 +486,9 @@
       <c r="C3" t="n">
         <v>3</v>
       </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -490,6 +502,9 @@
       <c r="C4" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="D4" s="1" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -503,6 +518,9 @@
       <c r="C5" t="n">
         <v>5</v>
       </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -516,6 +534,9 @@
       <c r="C6" t="n">
         <v>3</v>
       </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -527,6 +548,9 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
         <v>4</v>
       </c>
     </row>
@@ -536,6 +560,9 @@
       </c>
       <c r="C8" s="2" t="n">
         <v>32</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -58,10 +64,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,13 +434,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -457,6 +465,11 @@
           <t>07.07 09:00</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>07.07 09:30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -473,6 +486,9 @@
       <c r="D2" t="n">
         <v>7</v>
       </c>
+      <c r="E2" s="1" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -489,6 +505,9 @@
       <c r="D3" t="n">
         <v>3</v>
       </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -499,11 +518,14 @@
       <c r="B4" t="n">
         <v>9</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="2" t="n">
         <v>11</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -521,6 +543,9 @@
       <c r="D5" t="n">
         <v>5</v>
       </c>
+      <c r="E5" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -537,6 +562,9 @@
       <c r="D6" t="n">
         <v>3</v>
       </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -553,16 +581,22 @@
       <c r="D7" t="n">
         <v>4</v>
       </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>33</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -442,6 +442,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,6 +471,11 @@
           <t>07.07 09:30</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>07.07 10:40</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +495,9 @@
       <c r="E2" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="F2" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -508,6 +517,9 @@
       <c r="E3" t="n">
         <v>3</v>
       </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -527,6 +539,9 @@
       <c r="E4" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -546,6 +561,9 @@
       <c r="E5" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="F5" s="2" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -565,6 +583,9 @@
       <c r="E6" t="n">
         <v>3</v>
       </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -582,6 +603,9 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
         <v>4</v>
       </c>
     </row>
@@ -597,6 +621,9 @@
       </c>
       <c r="E8" s="3" t="n">
         <v>36</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -443,6 +443,7 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,6 +477,11 @@
           <t>07.07 10:40</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>07.07 13:30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -498,6 +504,9 @@
       <c r="F2" t="n">
         <v>8</v>
       </c>
+      <c r="G2" s="1" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -520,6 +529,9 @@
       <c r="F3" t="n">
         <v>3</v>
       </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -542,6 +554,9 @@
       <c r="F4" t="n">
         <v>12</v>
       </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -564,6 +579,9 @@
       <c r="F5" s="2" t="n">
         <v>7</v>
       </c>
+      <c r="G5" s="1" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -586,6 +604,9 @@
       <c r="F6" t="n">
         <v>3</v>
       </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -607,6 +628,9 @@
       </c>
       <c r="F7" t="n">
         <v>4</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -624,6 +648,9 @@
       </c>
       <c r="F8" s="3" t="n">
         <v>37</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,6 +483,11 @@
           <t>07.07 13:30</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>07.07 18:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -507,6 +513,9 @@
       <c r="G2" s="1" t="n">
         <v>9</v>
       </c>
+      <c r="H2" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -532,6 +541,9 @@
       <c r="G3" t="n">
         <v>3</v>
       </c>
+      <c r="H3" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -557,6 +569,9 @@
       <c r="G4" t="n">
         <v>12</v>
       </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -582,6 +597,9 @@
       <c r="G5" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -607,6 +625,9 @@
       <c r="G6" t="n">
         <v>3</v>
       </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -630,6 +651,9 @@
         <v>4</v>
       </c>
       <c r="G7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -651,6 +675,9 @@
       </c>
       <c r="G8" s="3" t="n">
         <v>40</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -445,6 +445,7 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,6 +489,11 @@
           <t>07.07 18:00</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>09.07 06:20</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -516,6 +522,9 @@
       <c r="H2" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="I2" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -544,6 +553,9 @@
       <c r="H3" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -572,6 +584,9 @@
       <c r="H4" t="n">
         <v>12</v>
       </c>
+      <c r="I4" s="1" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -600,6 +615,9 @@
       <c r="H5" t="n">
         <v>8</v>
       </c>
+      <c r="I5" s="1" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -628,6 +646,9 @@
       <c r="H6" t="n">
         <v>3</v>
       </c>
+      <c r="I6" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -654,6 +675,9 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -678,6 +702,9 @@
       </c>
       <c r="H8" s="3" t="n">
         <v>42</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -26,24 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
-        <bgColor rgb="00FF0000"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -64,11 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,18 +420,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="66" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -456,255 +435,203 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>06.07 16:48</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>07.07 06:25</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>07.07 09:00</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>07.07 09:30</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>07.07 10:40</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>07.07 13:30</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>07.07 18:00</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>09.07 06:20</t>
+          <t>10.07 09:59</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Волшебник Костя</t>
+          <t>Так и живём</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="I2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>32 мая</t>
+          <t>Верная жена</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Никого не жалко, никого.</t>
+          <t>Больно</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="F4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Три такта вальса «Достучаться до небес»</t>
+          <t>Обратите внимание на цветы</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="H5" t="n">
-        <v>8</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Олежек.</t>
+          <t>Последний свидетель</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Я из тех, кто.</t>
+          <t>Как Васька Косой на рыбалку пошёл, чтобы отдохнуть от жены мымры</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Стручок акации</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Мы любим вовсе не тех</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Итагин – железный дракон</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Виртуальный коньяк</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>4</v>
       </c>
-      <c r="C7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>45</v>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Апгрейд</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Перевод</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Мраморная говядина</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Я целую небо</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Цирк уехал, клоуны остались</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Как разбудить демона</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ника</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Бломпль</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Квантовый полиморф Умозрихина</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="1" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -52,9 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,11 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -438,6 +446,11 @@
           <t>10.07 09:59</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>10.07 10:30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -448,6 +461,9 @@
       <c r="B2" t="n">
         <v>2</v>
       </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -458,6 +474,9 @@
       <c r="B3" t="n">
         <v>0</v>
       </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -468,6 +487,9 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -478,6 +500,9 @@
       <c r="B5" t="n">
         <v>0</v>
       </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -488,6 +513,9 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -498,6 +526,9 @@
       <c r="B7" t="n">
         <v>0</v>
       </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -508,6 +539,9 @@
       <c r="B8" t="n">
         <v>0</v>
       </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -518,6 +552,9 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -528,6 +565,9 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -538,6 +578,9 @@
       <c r="B11" t="n">
         <v>4</v>
       </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -548,6 +591,9 @@
       <c r="B12" t="n">
         <v>0</v>
       </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -558,6 +604,9 @@
       <c r="B13" t="n">
         <v>0</v>
       </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -568,6 +617,9 @@
       <c r="B14" t="n">
         <v>1</v>
       </c>
+      <c r="C14" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -578,6 +630,9 @@
       <c r="B15" t="n">
         <v>0</v>
       </c>
+      <c r="C15" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -588,6 +643,9 @@
       <c r="B16" t="n">
         <v>0</v>
       </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -598,6 +656,9 @@
       <c r="B17" t="n">
         <v>1</v>
       </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -608,6 +669,9 @@
       <c r="B18" t="n">
         <v>1</v>
       </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -618,6 +682,9 @@
       <c r="B19" t="n">
         <v>0</v>
       </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -628,10 +695,16 @@
       <c r="B20" t="n">
         <v>1</v>
       </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>14</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -37,6 +37,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFF00"/>
         <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -58,10 +64,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,12 +434,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,6 +459,11 @@
           <t>10.07 10:30</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>10.07 11:05</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -464,6 +477,9 @@
       <c r="C2" t="n">
         <v>2</v>
       </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -477,6 +493,9 @@
       <c r="C3" t="n">
         <v>0</v>
       </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -490,6 +509,9 @@
       <c r="C4" t="n">
         <v>1</v>
       </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -503,6 +525,9 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -516,6 +541,9 @@
       <c r="C6" t="n">
         <v>1</v>
       </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -529,6 +557,9 @@
       <c r="C7" t="n">
         <v>0</v>
       </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -542,6 +573,9 @@
       <c r="C8" t="n">
         <v>0</v>
       </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -555,6 +589,9 @@
       <c r="C9" t="n">
         <v>1</v>
       </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -568,6 +605,9 @@
       <c r="C10" t="n">
         <v>1</v>
       </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -581,6 +621,9 @@
       <c r="C11" t="n">
         <v>4</v>
       </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -594,6 +637,9 @@
       <c r="C12" t="n">
         <v>0</v>
       </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -607,6 +653,9 @@
       <c r="C13" t="n">
         <v>0</v>
       </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -620,6 +669,9 @@
       <c r="C14" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -633,6 +685,9 @@
       <c r="C15" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -646,6 +701,9 @@
       <c r="C16" t="n">
         <v>0</v>
       </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -659,6 +717,9 @@
       <c r="C17" t="n">
         <v>1</v>
       </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -672,6 +733,9 @@
       <c r="C18" t="n">
         <v>1</v>
       </c>
+      <c r="D18" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -685,6 +749,9 @@
       <c r="C19" t="n">
         <v>0</v>
       </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -698,13 +765,19 @@
       <c r="C20" t="n">
         <v>1</v>
       </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="2" t="n">
+      <c r="B21" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C21" s="3" t="n">
         <v>16</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,13 +434,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,6 +465,11 @@
           <t>10.07 11:05</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>10.07 12:05</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -480,6 +486,9 @@
       <c r="D2" t="n">
         <v>2</v>
       </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,6 +505,9 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -512,6 +524,9 @@
       <c r="D4" t="n">
         <v>1</v>
       </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -528,6 +543,9 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -544,6 +562,9 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -560,6 +581,9 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -576,6 +600,9 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -592,6 +619,9 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -608,6 +638,9 @@
       <c r="D10" t="n">
         <v>1</v>
       </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -624,6 +657,9 @@
       <c r="D11" t="n">
         <v>4</v>
       </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -640,6 +676,9 @@
       <c r="D12" t="n">
         <v>0</v>
       </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -656,6 +695,9 @@
       <c r="D13" t="n">
         <v>0</v>
       </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -672,6 +714,9 @@
       <c r="D14" t="n">
         <v>2</v>
       </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -688,6 +733,9 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -704,6 +752,9 @@
       <c r="D16" t="n">
         <v>0</v>
       </c>
+      <c r="E16" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -720,6 +771,9 @@
       <c r="D17" t="n">
         <v>1</v>
       </c>
+      <c r="E17" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -736,6 +790,9 @@
       <c r="D18" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -752,6 +809,9 @@
       <c r="D19" t="n">
         <v>0</v>
       </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -766,6 +826,9 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -778,6 +841,9 @@
       </c>
       <c r="D21" s="3" t="n">
         <v>17</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -442,6 +442,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,6 +471,11 @@
           <t>10.07 12:05</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>10.07 12:25</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +495,9 @@
       <c r="E2" t="n">
         <v>2</v>
       </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -508,6 +517,9 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -527,6 +539,9 @@
       <c r="E4" t="n">
         <v>1</v>
       </c>
+      <c r="F4" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -546,6 +561,9 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -565,6 +583,9 @@
       <c r="E6" t="n">
         <v>1</v>
       </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -584,6 +605,9 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -603,6 +627,9 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -622,6 +649,9 @@
       <c r="E9" t="n">
         <v>1</v>
       </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -641,6 +671,9 @@
       <c r="E10" t="n">
         <v>1</v>
       </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -660,6 +693,9 @@
       <c r="E11" t="n">
         <v>4</v>
       </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -679,6 +715,9 @@
       <c r="E12" t="n">
         <v>0</v>
       </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -698,6 +737,9 @@
       <c r="E13" t="n">
         <v>0</v>
       </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -717,6 +759,9 @@
       <c r="E14" t="n">
         <v>2</v>
       </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -736,6 +781,9 @@
       <c r="E15" t="n">
         <v>1</v>
       </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -755,6 +803,9 @@
       <c r="E16" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -774,6 +825,9 @@
       <c r="E17" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -793,6 +847,9 @@
       <c r="E18" t="n">
         <v>2</v>
       </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -812,6 +869,9 @@
       <c r="E19" t="n">
         <v>0</v>
       </c>
+      <c r="F19" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -829,6 +889,9 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -844,6 +907,9 @@
       </c>
       <c r="E21" s="3" t="n">
         <v>19</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -443,6 +443,7 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,6 +477,11 @@
           <t>10.07 12:25</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>10.07 12:28</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -498,6 +504,9 @@
       <c r="F2" t="n">
         <v>2</v>
       </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -520,6 +529,9 @@
       <c r="F3" t="n">
         <v>0</v>
       </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -542,6 +554,9 @@
       <c r="F4" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="G4" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -564,6 +579,9 @@
       <c r="F5" t="n">
         <v>0</v>
       </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -586,6 +604,9 @@
       <c r="F6" t="n">
         <v>1</v>
       </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -608,6 +629,9 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -630,6 +654,9 @@
       <c r="F8" t="n">
         <v>0</v>
       </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -652,6 +679,9 @@
       <c r="F9" t="n">
         <v>1</v>
       </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -674,6 +704,9 @@
       <c r="F10" t="n">
         <v>1</v>
       </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -696,6 +729,9 @@
       <c r="F11" t="n">
         <v>4</v>
       </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -718,6 +754,9 @@
       <c r="F12" t="n">
         <v>0</v>
       </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -740,6 +779,9 @@
       <c r="F13" t="n">
         <v>0</v>
       </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -762,6 +804,9 @@
       <c r="F14" t="n">
         <v>2</v>
       </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -784,6 +829,9 @@
       <c r="F15" t="n">
         <v>1</v>
       </c>
+      <c r="G15" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -806,6 +854,9 @@
       <c r="F16" t="n">
         <v>1</v>
       </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -828,6 +879,9 @@
       <c r="F17" t="n">
         <v>2</v>
       </c>
+      <c r="G17" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -850,6 +904,9 @@
       <c r="F18" t="n">
         <v>2</v>
       </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -872,6 +929,9 @@
       <c r="F19" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -892,6 +952,9 @@
         <v>1</v>
       </c>
       <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -910,6 +973,9 @@
       </c>
       <c r="F21" s="3" t="n">
         <v>21</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,6 +483,11 @@
           <t>10.07 12:28</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>10.07 13:06</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -507,6 +513,9 @@
       <c r="G2" t="n">
         <v>2</v>
       </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -532,6 +541,9 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
+      <c r="H3" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -557,6 +569,9 @@
       <c r="G4" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -582,6 +597,9 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -607,6 +625,9 @@
       <c r="G6" t="n">
         <v>1</v>
       </c>
+      <c r="H6" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -632,6 +653,9 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -657,6 +681,9 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -682,6 +709,9 @@
       <c r="G9" t="n">
         <v>1</v>
       </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -707,6 +737,9 @@
       <c r="G10" t="n">
         <v>1</v>
       </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -732,6 +765,9 @@
       <c r="G11" t="n">
         <v>4</v>
       </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -757,6 +793,9 @@
       <c r="G12" t="n">
         <v>0</v>
       </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -782,6 +821,9 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -807,6 +849,9 @@
       <c r="G14" t="n">
         <v>2</v>
       </c>
+      <c r="H14" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -832,6 +877,9 @@
       <c r="G15" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -857,6 +905,9 @@
       <c r="G16" t="n">
         <v>1</v>
       </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -882,6 +933,9 @@
       <c r="G17" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -907,6 +961,9 @@
       <c r="G18" t="n">
         <v>2</v>
       </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -932,6 +989,9 @@
       <c r="G19" t="n">
         <v>1</v>
       </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -955,6 +1015,9 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -976,6 +1039,9 @@
       </c>
       <c r="G21" s="3" t="n">
         <v>24</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -445,6 +445,7 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,6 +489,11 @@
           <t>10.07 13:06</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>10.07 13:09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -516,6 +522,9 @@
       <c r="H2" t="n">
         <v>2</v>
       </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -544,6 +553,9 @@
       <c r="H3" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -572,6 +584,9 @@
       <c r="H4" t="n">
         <v>3</v>
       </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -600,6 +615,9 @@
       <c r="H5" t="n">
         <v>0</v>
       </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -628,6 +646,9 @@
       <c r="H6" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -656,6 +677,9 @@
       <c r="H7" t="n">
         <v>0</v>
       </c>
+      <c r="I7" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -684,6 +708,9 @@
       <c r="H8" t="n">
         <v>0</v>
       </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -712,6 +739,9 @@
       <c r="H9" t="n">
         <v>1</v>
       </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -740,6 +770,9 @@
       <c r="H10" t="n">
         <v>1</v>
       </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -768,6 +801,9 @@
       <c r="H11" t="n">
         <v>4</v>
       </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -796,6 +832,9 @@
       <c r="H12" t="n">
         <v>0</v>
       </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -824,6 +863,9 @@
       <c r="H13" t="n">
         <v>0</v>
       </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -852,6 +894,9 @@
       <c r="H14" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -880,6 +925,9 @@
       <c r="H15" t="n">
         <v>2</v>
       </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -908,6 +956,9 @@
       <c r="H16" t="n">
         <v>1</v>
       </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -936,6 +987,9 @@
       <c r="H17" t="n">
         <v>3</v>
       </c>
+      <c r="I17" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -964,6 +1018,9 @@
       <c r="H18" t="n">
         <v>2</v>
       </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -992,6 +1049,9 @@
       <c r="H19" t="n">
         <v>1</v>
       </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1018,6 +1078,9 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1042,6 +1105,9 @@
       </c>
       <c r="H21" s="3" t="n">
         <v>27</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -446,6 +446,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,6 +495,11 @@
           <t>10.07 13:09</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>10.07 13:17</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -525,6 +531,9 @@
       <c r="I2" t="n">
         <v>2</v>
       </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -556,6 +565,9 @@
       <c r="I3" t="n">
         <v>1</v>
       </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -587,6 +599,9 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
+      <c r="J4" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -618,6 +633,9 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -649,6 +667,9 @@
       <c r="I6" t="n">
         <v>2</v>
       </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -680,6 +701,9 @@
       <c r="I7" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -711,6 +735,9 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -742,6 +769,9 @@
       <c r="I9" t="n">
         <v>1</v>
       </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -773,6 +803,9 @@
       <c r="I10" t="n">
         <v>1</v>
       </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -804,6 +837,9 @@
       <c r="I11" t="n">
         <v>4</v>
       </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -835,6 +871,9 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -866,6 +905,9 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -897,6 +939,9 @@
       <c r="I14" t="n">
         <v>3</v>
       </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -928,6 +973,9 @@
       <c r="I15" t="n">
         <v>2</v>
       </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -959,6 +1007,9 @@
       <c r="I16" t="n">
         <v>1</v>
       </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -990,6 +1041,9 @@
       <c r="I17" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1021,6 +1075,9 @@
       <c r="I18" t="n">
         <v>2</v>
       </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1052,6 +1109,9 @@
       <c r="I19" t="n">
         <v>1</v>
       </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1082,6 +1142,9 @@
       </c>
       <c r="I20" t="n">
         <v>1</v>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1108,6 +1171,9 @@
       </c>
       <c r="I21" s="3" t="n">
         <v>29</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -447,6 +447,7 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,6 +501,11 @@
           <t>10.07 13:17</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>10.07 13:49</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,6 +540,9 @@
       <c r="J2" t="n">
         <v>2</v>
       </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -568,6 +577,9 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -602,6 +614,9 @@
       <c r="J4" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -636,6 +651,9 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -670,6 +688,9 @@
       <c r="J6" t="n">
         <v>2</v>
       </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -704,6 +725,9 @@
       <c r="J7" t="n">
         <v>1</v>
       </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -738,6 +762,9 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -772,6 +799,9 @@
       <c r="J9" t="n">
         <v>1</v>
       </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -806,6 +836,9 @@
       <c r="J10" t="n">
         <v>1</v>
       </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -840,6 +873,9 @@
       <c r="J11" t="n">
         <v>4</v>
       </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -874,6 +910,9 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -908,6 +947,9 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -942,6 +984,9 @@
       <c r="J14" t="n">
         <v>3</v>
       </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -976,6 +1021,9 @@
       <c r="J15" t="n">
         <v>2</v>
       </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1010,6 +1058,9 @@
       <c r="J16" t="n">
         <v>1</v>
       </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1044,6 +1095,9 @@
       <c r="J17" t="n">
         <v>4</v>
       </c>
+      <c r="K17" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1078,6 +1132,9 @@
       <c r="J18" t="n">
         <v>2</v>
       </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1112,6 +1169,9 @@
       <c r="J19" t="n">
         <v>1</v>
       </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1145,6 +1205,9 @@
       </c>
       <c r="J20" s="1" t="n">
         <v>2</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1174,6 +1237,9 @@
       </c>
       <c r="J21" s="3" t="n">
         <v>31</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -448,6 +448,7 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,6 +507,11 @@
           <t>10.07 13:49</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>10.07 16:49</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -543,6 +549,9 @@
       <c r="K2" t="n">
         <v>2</v>
       </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -580,6 +589,9 @@
       <c r="K3" t="n">
         <v>1</v>
       </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -617,6 +629,9 @@
       <c r="K4" t="n">
         <v>4</v>
       </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -654,6 +669,9 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -691,6 +709,9 @@
       <c r="K6" t="n">
         <v>2</v>
       </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -728,6 +749,9 @@
       <c r="K7" t="n">
         <v>1</v>
       </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -765,6 +789,9 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -802,6 +829,9 @@
       <c r="K9" t="n">
         <v>1</v>
       </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -839,6 +869,9 @@
       <c r="K10" t="n">
         <v>1</v>
       </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -876,6 +909,9 @@
       <c r="K11" t="n">
         <v>4</v>
       </c>
+      <c r="L11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -913,6 +949,9 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -950,6 +989,9 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
+      <c r="L13" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -987,6 +1029,9 @@
       <c r="K14" t="n">
         <v>3</v>
       </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1024,6 +1069,9 @@
       <c r="K15" t="n">
         <v>2</v>
       </c>
+      <c r="L15" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1061,6 +1109,9 @@
       <c r="K16" t="n">
         <v>1</v>
       </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1098,6 +1149,9 @@
       <c r="K17" t="n">
         <v>4</v>
       </c>
+      <c r="L17" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1135,6 +1189,9 @@
       <c r="K18" t="n">
         <v>2</v>
       </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1172,6 +1229,9 @@
       <c r="K19" t="n">
         <v>1</v>
       </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1207,6 +1267,9 @@
         <v>2</v>
       </c>
       <c r="K20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1240,6 +1303,9 @@
       </c>
       <c r="K21" s="3" t="n">
         <v>32</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -449,6 +449,7 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,6 +513,11 @@
           <t>10.07 16:49</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>10.07 16:52</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -552,6 +558,9 @@
       <c r="L2" t="n">
         <v>2</v>
       </c>
+      <c r="M2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -592,6 +601,9 @@
       <c r="L3" t="n">
         <v>1</v>
       </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -632,6 +644,9 @@
       <c r="L4" t="n">
         <v>4</v>
       </c>
+      <c r="M4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -672,6 +687,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -712,6 +730,9 @@
       <c r="L6" t="n">
         <v>2</v>
       </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -752,6 +773,9 @@
       <c r="L7" t="n">
         <v>1</v>
       </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -792,6 +816,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -832,6 +859,9 @@
       <c r="L9" t="n">
         <v>1</v>
       </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -872,6 +902,9 @@
       <c r="L10" t="n">
         <v>1</v>
       </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -912,6 +945,9 @@
       <c r="L11" t="n">
         <v>4</v>
       </c>
+      <c r="M11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -952,6 +988,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -992,6 +1031,9 @@
       <c r="L13" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="M13" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1032,6 +1074,9 @@
       <c r="L14" t="n">
         <v>3</v>
       </c>
+      <c r="M14" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1072,6 +1117,9 @@
       <c r="L15" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="M15" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1112,6 +1160,9 @@
       <c r="L16" t="n">
         <v>1</v>
       </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1152,6 +1203,9 @@
       <c r="L17" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="M17" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1192,6 +1246,9 @@
       <c r="L18" t="n">
         <v>2</v>
       </c>
+      <c r="M18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1232,6 +1289,9 @@
       <c r="L19" t="n">
         <v>1</v>
       </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1270,6 +1330,9 @@
         <v>3</v>
       </c>
       <c r="L20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1306,6 +1369,9 @@
       </c>
       <c r="L21" s="3" t="n">
         <v>35</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -450,6 +450,7 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -518,6 +519,11 @@
           <t>10.07 16:52</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>10.07 17:04</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -561,6 +567,9 @@
       <c r="M2" t="n">
         <v>2</v>
       </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -604,6 +613,9 @@
       <c r="M3" t="n">
         <v>1</v>
       </c>
+      <c r="N3" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -647,6 +659,9 @@
       <c r="M4" t="n">
         <v>4</v>
       </c>
+      <c r="N4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -690,6 +705,9 @@
       <c r="M5" t="n">
         <v>0</v>
       </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -733,6 +751,9 @@
       <c r="M6" t="n">
         <v>2</v>
       </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -776,6 +797,9 @@
       <c r="M7" t="n">
         <v>1</v>
       </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -819,6 +843,9 @@
       <c r="M8" t="n">
         <v>0</v>
       </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -862,6 +889,9 @@
       <c r="M9" t="n">
         <v>1</v>
       </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -905,6 +935,9 @@
       <c r="M10" t="n">
         <v>1</v>
       </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -948,6 +981,9 @@
       <c r="M11" t="n">
         <v>4</v>
       </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -991,6 +1027,9 @@
       <c r="M12" t="n">
         <v>0</v>
       </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1034,6 +1073,9 @@
       <c r="M13" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1077,6 +1119,9 @@
       <c r="M14" t="n">
         <v>3</v>
       </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1120,6 +1165,9 @@
       <c r="M15" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="N15" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1163,6 +1211,9 @@
       <c r="M16" t="n">
         <v>1</v>
       </c>
+      <c r="N16" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1206,6 +1257,9 @@
       <c r="M17" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="N17" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1249,6 +1303,9 @@
       <c r="M18" t="n">
         <v>2</v>
       </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1292,6 +1349,9 @@
       <c r="M19" t="n">
         <v>1</v>
       </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1333,6 +1393,9 @@
         <v>3</v>
       </c>
       <c r="M20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1372,6 +1435,9 @@
       </c>
       <c r="M21" s="3" t="n">
         <v>38</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,7 @@
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -524,6 +525,11 @@
           <t>10.07 17:04</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>10.07 17:13</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -570,6 +576,9 @@
       <c r="N2" t="n">
         <v>2</v>
       </c>
+      <c r="O2" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -616,6 +625,9 @@
       <c r="N3" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -662,6 +674,9 @@
       <c r="N4" t="n">
         <v>4</v>
       </c>
+      <c r="O4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -708,6 +723,9 @@
       <c r="N5" t="n">
         <v>0</v>
       </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -754,6 +772,9 @@
       <c r="N6" t="n">
         <v>2</v>
       </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -800,6 +821,9 @@
       <c r="N7" t="n">
         <v>1</v>
       </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -846,6 +870,9 @@
       <c r="N8" t="n">
         <v>0</v>
       </c>
+      <c r="O8" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -892,6 +919,9 @@
       <c r="N9" t="n">
         <v>1</v>
       </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -938,6 +968,9 @@
       <c r="N10" t="n">
         <v>1</v>
       </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -984,6 +1017,9 @@
       <c r="N11" t="n">
         <v>4</v>
       </c>
+      <c r="O11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1030,6 +1066,9 @@
       <c r="N12" t="n">
         <v>0</v>
       </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1076,6 +1115,9 @@
       <c r="N13" t="n">
         <v>2</v>
       </c>
+      <c r="O13" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1122,6 +1164,9 @@
       <c r="N14" t="n">
         <v>3</v>
       </c>
+      <c r="O14" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1168,6 +1213,9 @@
       <c r="N15" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="O15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1214,6 +1262,9 @@
       <c r="N16" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="O16" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1260,6 +1311,9 @@
       <c r="N17" t="n">
         <v>6</v>
       </c>
+      <c r="O17" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1306,6 +1360,9 @@
       <c r="N18" t="n">
         <v>2</v>
       </c>
+      <c r="O18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1352,6 +1409,9 @@
       <c r="N19" t="n">
         <v>1</v>
       </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1396,6 +1456,9 @@
         <v>3</v>
       </c>
       <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1438,6 +1501,9 @@
       </c>
       <c r="N21" s="3" t="n">
         <v>41</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -452,6 +452,7 @@
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,6 +531,11 @@
           <t>10.07 17:13</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>10.07 18:28</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -579,6 +585,9 @@
       <c r="O2" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="P2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -628,6 +637,9 @@
       <c r="O3" t="n">
         <v>2</v>
       </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -677,6 +689,9 @@
       <c r="O4" t="n">
         <v>4</v>
       </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -726,6 +741,9 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -775,6 +793,9 @@
       <c r="O6" t="n">
         <v>2</v>
       </c>
+      <c r="P6" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -824,6 +845,9 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -873,6 +897,9 @@
       <c r="O8" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="P8" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -922,6 +949,9 @@
       <c r="O9" t="n">
         <v>1</v>
       </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -971,6 +1001,9 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1020,6 +1053,9 @@
       <c r="O11" t="n">
         <v>4</v>
       </c>
+      <c r="P11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1069,6 +1105,9 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1118,6 +1157,9 @@
       <c r="O13" t="n">
         <v>2</v>
       </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1167,6 +1209,9 @@
       <c r="O14" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="P14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1216,6 +1261,9 @@
       <c r="O15" t="n">
         <v>5</v>
       </c>
+      <c r="P15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1265,6 +1313,9 @@
       <c r="O16" t="n">
         <v>2</v>
       </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1314,6 +1365,9 @@
       <c r="O17" t="n">
         <v>6</v>
       </c>
+      <c r="P17" s="1" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1363,6 +1417,9 @@
       <c r="O18" t="n">
         <v>2</v>
       </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1412,6 +1469,9 @@
       <c r="O19" t="n">
         <v>1</v>
       </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1459,6 +1519,9 @@
         <v>3</v>
       </c>
       <c r="O20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1504,6 +1567,9 @@
       </c>
       <c r="O21" s="3" t="n">
         <v>44</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -453,6 +453,7 @@
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -536,6 +537,11 @@
           <t>10.07 18:28</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>10.07 20:59</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -588,6 +594,9 @@
       <c r="P2" t="n">
         <v>3</v>
       </c>
+      <c r="Q2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -640,6 +649,9 @@
       <c r="P3" t="n">
         <v>2</v>
       </c>
+      <c r="Q3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -692,6 +704,9 @@
       <c r="P4" t="n">
         <v>4</v>
       </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -744,6 +759,9 @@
       <c r="P5" t="n">
         <v>0</v>
       </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -796,6 +814,9 @@
       <c r="P6" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -848,6 +869,9 @@
       <c r="P7" t="n">
         <v>1</v>
       </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -900,6 +924,9 @@
       <c r="P8" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -952,6 +979,9 @@
       <c r="P9" t="n">
         <v>1</v>
       </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1004,6 +1034,9 @@
       <c r="P10" t="n">
         <v>1</v>
       </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1056,6 +1089,9 @@
       <c r="P11" t="n">
         <v>4</v>
       </c>
+      <c r="Q11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1108,6 +1144,9 @@
       <c r="P12" t="n">
         <v>0</v>
       </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1160,6 +1199,9 @@
       <c r="P13" t="n">
         <v>2</v>
       </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1212,6 +1254,9 @@
       <c r="P14" t="n">
         <v>4</v>
       </c>
+      <c r="Q14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1264,6 +1309,9 @@
       <c r="P15" t="n">
         <v>5</v>
       </c>
+      <c r="Q15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1316,6 +1364,9 @@
       <c r="P16" t="n">
         <v>2</v>
       </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1368,6 +1419,9 @@
       <c r="P17" s="1" t="n">
         <v>7</v>
       </c>
+      <c r="Q17" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1420,6 +1474,9 @@
       <c r="P18" t="n">
         <v>2</v>
       </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1472,6 +1529,9 @@
       <c r="P19" t="n">
         <v>1</v>
       </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1523,6 +1583,9 @@
       </c>
       <c r="P20" t="n">
         <v>3</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1570,6 +1633,9 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>47</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -454,6 +454,7 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,6 +543,11 @@
           <t>10.07 20:59</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>10.07 22:19</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -597,6 +603,9 @@
       <c r="Q2" t="n">
         <v>3</v>
       </c>
+      <c r="R2" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -652,6 +661,9 @@
       <c r="Q3" t="n">
         <v>2</v>
       </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -707,6 +719,9 @@
       <c r="Q4" t="n">
         <v>4</v>
       </c>
+      <c r="R4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -762,6 +777,9 @@
       <c r="Q5" t="n">
         <v>0</v>
       </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -817,6 +835,9 @@
       <c r="Q6" t="n">
         <v>3</v>
       </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -872,6 +893,9 @@
       <c r="Q7" t="n">
         <v>1</v>
       </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -927,6 +951,9 @@
       <c r="Q8" t="n">
         <v>2</v>
       </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -982,6 +1009,9 @@
       <c r="Q9" t="n">
         <v>1</v>
       </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1037,6 +1067,9 @@
       <c r="Q10" t="n">
         <v>1</v>
       </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1092,6 +1125,9 @@
       <c r="Q11" t="n">
         <v>4</v>
       </c>
+      <c r="R11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1147,6 +1183,9 @@
       <c r="Q12" t="n">
         <v>0</v>
       </c>
+      <c r="R12" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1202,6 +1241,9 @@
       <c r="Q13" t="n">
         <v>2</v>
       </c>
+      <c r="R13" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1257,6 +1299,9 @@
       <c r="Q14" t="n">
         <v>4</v>
       </c>
+      <c r="R14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1312,6 +1357,9 @@
       <c r="Q15" t="n">
         <v>5</v>
       </c>
+      <c r="R15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1367,6 +1415,9 @@
       <c r="Q16" t="n">
         <v>2</v>
       </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1422,6 +1473,9 @@
       <c r="Q17" t="n">
         <v>7</v>
       </c>
+      <c r="R17" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1477,6 +1531,9 @@
       <c r="Q18" t="n">
         <v>2</v>
       </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1532,6 +1589,9 @@
       <c r="Q19" t="n">
         <v>1</v>
       </c>
+      <c r="R19" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1585,6 +1645,9 @@
         <v>3</v>
       </c>
       <c r="Q20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1636,6 +1699,9 @@
       </c>
       <c r="Q21" s="3" t="n">
         <v>48</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -455,6 +455,7 @@
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -548,6 +549,11 @@
           <t>10.07 22:19</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>10.07 22:44</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -606,6 +612,9 @@
       <c r="R2" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="S2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -664,6 +673,9 @@
       <c r="R3" t="n">
         <v>2</v>
       </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -722,6 +734,9 @@
       <c r="R4" t="n">
         <v>4</v>
       </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -780,6 +795,9 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -838,6 +856,9 @@
       <c r="R6" t="n">
         <v>3</v>
       </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -896,6 +917,9 @@
       <c r="R7" t="n">
         <v>1</v>
       </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -954,6 +978,9 @@
       <c r="R8" t="n">
         <v>2</v>
       </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1012,6 +1039,9 @@
       <c r="R9" t="n">
         <v>1</v>
       </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1070,6 +1100,9 @@
       <c r="R10" t="n">
         <v>1</v>
       </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1128,6 +1161,9 @@
       <c r="R11" t="n">
         <v>4</v>
       </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1186,6 +1222,9 @@
       <c r="R12" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1244,6 +1283,9 @@
       <c r="R13" t="n">
         <v>2</v>
       </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1302,6 +1344,9 @@
       <c r="R14" t="n">
         <v>4</v>
       </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1360,6 +1405,9 @@
       <c r="R15" t="n">
         <v>5</v>
       </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1418,6 +1466,9 @@
       <c r="R16" t="n">
         <v>2</v>
       </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1476,6 +1527,9 @@
       <c r="R17" t="n">
         <v>7</v>
       </c>
+      <c r="S17" s="2" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1534,6 +1588,9 @@
       <c r="R18" t="n">
         <v>2</v>
       </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1592,6 +1649,9 @@
       <c r="R19" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1648,6 +1708,9 @@
         <v>4</v>
       </c>
       <c r="R20" t="n">
+        <v>4</v>
+      </c>
+      <c r="S20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1702,6 +1765,9 @@
       </c>
       <c r="R21" s="3" t="n">
         <v>51</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -456,6 +456,7 @@
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -554,6 +555,11 @@
           <t>10.07 22:44</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>10.07 23:10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -615,6 +621,9 @@
       <c r="S2" t="n">
         <v>4</v>
       </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -676,6 +685,9 @@
       <c r="S3" t="n">
         <v>2</v>
       </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -737,6 +749,9 @@
       <c r="S4" t="n">
         <v>4</v>
       </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -798,6 +813,9 @@
       <c r="S5" t="n">
         <v>0</v>
       </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -859,6 +877,9 @@
       <c r="S6" t="n">
         <v>3</v>
       </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -920,6 +941,9 @@
       <c r="S7" t="n">
         <v>1</v>
       </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -981,6 +1005,9 @@
       <c r="S8" t="n">
         <v>2</v>
       </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1042,6 +1069,9 @@
       <c r="S9" t="n">
         <v>1</v>
       </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1103,6 +1133,9 @@
       <c r="S10" t="n">
         <v>1</v>
       </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1164,6 +1197,9 @@
       <c r="S11" t="n">
         <v>4</v>
       </c>
+      <c r="T11" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1225,6 +1261,9 @@
       <c r="S12" t="n">
         <v>1</v>
       </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1286,6 +1325,9 @@
       <c r="S13" t="n">
         <v>2</v>
       </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1347,6 +1389,9 @@
       <c r="S14" t="n">
         <v>4</v>
       </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1408,6 +1453,9 @@
       <c r="S15" t="n">
         <v>5</v>
       </c>
+      <c r="T15" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1469,6 +1517,9 @@
       <c r="S16" t="n">
         <v>2</v>
       </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1530,6 +1581,9 @@
       <c r="S17" s="2" t="n">
         <v>8</v>
       </c>
+      <c r="T17" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1591,6 +1645,9 @@
       <c r="S18" t="n">
         <v>2</v>
       </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1652,6 +1709,9 @@
       <c r="S19" t="n">
         <v>2</v>
       </c>
+      <c r="T19" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1711,6 +1771,9 @@
         <v>4</v>
       </c>
       <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1768,6 +1831,9 @@
       </c>
       <c r="S21" s="3" t="n">
         <v>52</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -457,6 +457,7 @@
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -560,6 +561,11 @@
           <t>10.07 23:10</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>11.07 00:10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -624,6 +630,9 @@
       <c r="T2" t="n">
         <v>4</v>
       </c>
+      <c r="U2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -688,6 +697,9 @@
       <c r="T3" t="n">
         <v>2</v>
       </c>
+      <c r="U3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -752,6 +764,9 @@
       <c r="T4" t="n">
         <v>4</v>
       </c>
+      <c r="U4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -816,6 +831,9 @@
       <c r="T5" t="n">
         <v>0</v>
       </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -880,6 +898,9 @@
       <c r="T6" t="n">
         <v>3</v>
       </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -944,6 +965,9 @@
       <c r="T7" t="n">
         <v>1</v>
       </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1008,6 +1032,9 @@
       <c r="T8" t="n">
         <v>2</v>
       </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1072,6 +1099,9 @@
       <c r="T9" t="n">
         <v>1</v>
       </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1136,6 +1166,9 @@
       <c r="T10" t="n">
         <v>1</v>
       </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1200,6 +1233,9 @@
       <c r="T11" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="U11" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1264,6 +1300,9 @@
       <c r="T12" t="n">
         <v>1</v>
       </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1328,6 +1367,9 @@
       <c r="T13" t="n">
         <v>2</v>
       </c>
+      <c r="U13" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1392,6 +1434,9 @@
       <c r="T14" t="n">
         <v>4</v>
       </c>
+      <c r="U14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1456,6 +1501,9 @@
       <c r="T15" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="U15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1520,6 +1568,9 @@
       <c r="T16" t="n">
         <v>2</v>
       </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1584,6 +1635,9 @@
       <c r="T17" t="n">
         <v>8</v>
       </c>
+      <c r="U17" s="2" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1648,6 +1702,9 @@
       <c r="T18" t="n">
         <v>2</v>
       </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1712,6 +1769,9 @@
       <c r="T19" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="U19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1774,6 +1834,9 @@
         <v>4</v>
       </c>
       <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1834,6 +1897,9 @@
       </c>
       <c r="T21" s="3" t="n">
         <v>55</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -458,6 +458,7 @@
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -566,6 +567,11 @@
           <t>11.07 00:10</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>11.07 10:52</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -633,6 +639,9 @@
       <c r="U2" t="n">
         <v>4</v>
       </c>
+      <c r="V2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -700,6 +709,9 @@
       <c r="U3" t="n">
         <v>2</v>
       </c>
+      <c r="V3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -767,6 +779,9 @@
       <c r="U4" t="n">
         <v>4</v>
       </c>
+      <c r="V4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -834,6 +849,9 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -901,6 +919,9 @@
       <c r="U6" t="n">
         <v>3</v>
       </c>
+      <c r="V6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -968,6 +989,9 @@
       <c r="U7" t="n">
         <v>1</v>
       </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1035,6 +1059,9 @@
       <c r="U8" t="n">
         <v>2</v>
       </c>
+      <c r="V8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1102,6 +1129,9 @@
       <c r="U9" t="n">
         <v>1</v>
       </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1169,6 +1199,9 @@
       <c r="U10" t="n">
         <v>1</v>
       </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1236,6 +1269,9 @@
       <c r="U11" t="n">
         <v>5</v>
       </c>
+      <c r="V11" s="2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1303,6 +1339,9 @@
       <c r="U12" t="n">
         <v>1</v>
       </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1370,6 +1409,9 @@
       <c r="U13" t="n">
         <v>2</v>
       </c>
+      <c r="V13" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1437,6 +1479,9 @@
       <c r="U14" t="n">
         <v>4</v>
       </c>
+      <c r="V14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1504,6 +1549,9 @@
       <c r="U15" t="n">
         <v>6</v>
       </c>
+      <c r="V15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1571,6 +1619,9 @@
       <c r="U16" t="n">
         <v>2</v>
       </c>
+      <c r="V16" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1638,6 +1689,9 @@
       <c r="U17" s="2" t="n">
         <v>9</v>
       </c>
+      <c r="V17" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1705,6 +1759,9 @@
       <c r="U18" t="n">
         <v>2</v>
       </c>
+      <c r="V18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1772,6 +1829,9 @@
       <c r="U19" t="n">
         <v>3</v>
       </c>
+      <c r="V19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1837,6 +1897,9 @@
         <v>4</v>
       </c>
       <c r="U20" t="n">
+        <v>4</v>
+      </c>
+      <c r="V20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1900,6 +1963,9 @@
       </c>
       <c r="U21" s="3" t="n">
         <v>56</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -459,6 +459,7 @@
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -572,6 +573,11 @@
           <t>11.07 10:52</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>11.07 11:19</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -642,6 +648,9 @@
       <c r="V2" t="n">
         <v>4</v>
       </c>
+      <c r="W2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -712,6 +721,9 @@
       <c r="V3" t="n">
         <v>2</v>
       </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -782,6 +794,9 @@
       <c r="V4" t="n">
         <v>4</v>
       </c>
+      <c r="W4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -852,6 +867,9 @@
       <c r="V5" t="n">
         <v>0</v>
       </c>
+      <c r="W5" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -922,6 +940,9 @@
       <c r="V6" t="n">
         <v>3</v>
       </c>
+      <c r="W6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -992,6 +1013,9 @@
       <c r="V7" t="n">
         <v>1</v>
       </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1062,6 +1086,9 @@
       <c r="V8" t="n">
         <v>2</v>
       </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1132,6 +1159,9 @@
       <c r="V9" t="n">
         <v>1</v>
       </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1202,6 +1232,9 @@
       <c r="V10" t="n">
         <v>1</v>
       </c>
+      <c r="W10" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1272,6 +1305,9 @@
       <c r="V11" s="2" t="n">
         <v>6</v>
       </c>
+      <c r="W11" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1342,6 +1378,9 @@
       <c r="V12" t="n">
         <v>1</v>
       </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1412,6 +1451,9 @@
       <c r="V13" t="n">
         <v>2</v>
       </c>
+      <c r="W13" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1482,6 +1524,9 @@
       <c r="V14" t="n">
         <v>4</v>
       </c>
+      <c r="W14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1552,6 +1597,9 @@
       <c r="V15" t="n">
         <v>6</v>
       </c>
+      <c r="W15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1622,6 +1670,9 @@
       <c r="V16" t="n">
         <v>2</v>
       </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1692,6 +1743,9 @@
       <c r="V17" t="n">
         <v>9</v>
       </c>
+      <c r="W17" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1762,6 +1816,9 @@
       <c r="V18" t="n">
         <v>2</v>
       </c>
+      <c r="W18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1832,6 +1889,9 @@
       <c r="V19" t="n">
         <v>3</v>
       </c>
+      <c r="W19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1900,6 +1960,9 @@
         <v>4</v>
       </c>
       <c r="V20" t="n">
+        <v>4</v>
+      </c>
+      <c r="W20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1966,6 +2029,9 @@
       </c>
       <c r="V21" s="3" t="n">
         <v>57</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -460,6 +460,7 @@
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -578,6 +579,11 @@
           <t>11.07 11:19</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>11.07 14:31</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -651,6 +657,9 @@
       <c r="W2" t="n">
         <v>4</v>
       </c>
+      <c r="X2" s="2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -724,6 +733,9 @@
       <c r="W3" t="n">
         <v>2</v>
       </c>
+      <c r="X3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -797,6 +809,9 @@
       <c r="W4" t="n">
         <v>4</v>
       </c>
+      <c r="X4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -870,6 +885,9 @@
       <c r="W5" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -943,6 +961,9 @@
       <c r="W6" t="n">
         <v>3</v>
       </c>
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1016,6 +1037,9 @@
       <c r="W7" t="n">
         <v>1</v>
       </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1089,6 +1113,9 @@
       <c r="W8" t="n">
         <v>2</v>
       </c>
+      <c r="X8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1162,6 +1189,9 @@
       <c r="W9" t="n">
         <v>1</v>
       </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1235,6 +1265,9 @@
       <c r="W10" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1308,6 +1341,9 @@
       <c r="W11" t="n">
         <v>6</v>
       </c>
+      <c r="X11" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1381,6 +1417,9 @@
       <c r="W12" t="n">
         <v>1</v>
       </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1454,6 +1493,9 @@
       <c r="W13" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="X13" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1527,6 +1569,9 @@
       <c r="W14" t="n">
         <v>4</v>
       </c>
+      <c r="X14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1600,6 +1645,9 @@
       <c r="W15" t="n">
         <v>6</v>
       </c>
+      <c r="X15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1673,6 +1721,9 @@
       <c r="W16" t="n">
         <v>2</v>
       </c>
+      <c r="X16" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1746,6 +1797,9 @@
       <c r="W17" t="n">
         <v>9</v>
       </c>
+      <c r="X17" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1819,6 +1873,9 @@
       <c r="W18" t="n">
         <v>2</v>
       </c>
+      <c r="X18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1892,6 +1949,9 @@
       <c r="W19" t="n">
         <v>3</v>
       </c>
+      <c r="X19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1963,6 +2023,9 @@
         <v>4</v>
       </c>
       <c r="W20" t="n">
+        <v>4</v>
+      </c>
+      <c r="X20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2032,6 +2095,9 @@
       </c>
       <c r="W21" s="3" t="n">
         <v>60</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -461,6 +461,7 @@
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -584,6 +585,11 @@
           <t>11.07 14:31</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>12.07 11:22</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -660,6 +666,9 @@
       <c r="X2" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="Y2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -736,6 +745,9 @@
       <c r="X3" t="n">
         <v>2</v>
       </c>
+      <c r="Y3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -812,6 +824,9 @@
       <c r="X4" t="n">
         <v>4</v>
       </c>
+      <c r="Y4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -888,6 +903,9 @@
       <c r="X5" t="n">
         <v>1</v>
       </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -964,6 +982,9 @@
       <c r="X6" t="n">
         <v>3</v>
       </c>
+      <c r="Y6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1040,6 +1061,9 @@
       <c r="X7" t="n">
         <v>1</v>
       </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1116,6 +1140,9 @@
       <c r="X8" t="n">
         <v>2</v>
       </c>
+      <c r="Y8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1192,6 +1219,9 @@
       <c r="X9" t="n">
         <v>1</v>
       </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1268,6 +1298,9 @@
       <c r="X10" t="n">
         <v>2</v>
       </c>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1344,6 +1377,9 @@
       <c r="X11" t="n">
         <v>6</v>
       </c>
+      <c r="Y11" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1420,6 +1456,9 @@
       <c r="X12" t="n">
         <v>1</v>
       </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1496,6 +1535,9 @@
       <c r="X13" t="n">
         <v>3</v>
       </c>
+      <c r="Y13" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1572,6 +1614,9 @@
       <c r="X14" t="n">
         <v>4</v>
       </c>
+      <c r="Y14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1648,6 +1693,9 @@
       <c r="X15" t="n">
         <v>6</v>
       </c>
+      <c r="Y15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1724,6 +1772,9 @@
       <c r="X16" t="n">
         <v>2</v>
       </c>
+      <c r="Y16" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1800,6 +1851,9 @@
       <c r="X17" t="n">
         <v>9</v>
       </c>
+      <c r="Y17" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1876,6 +1930,9 @@
       <c r="X18" t="n">
         <v>2</v>
       </c>
+      <c r="Y18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1952,6 +2009,9 @@
       <c r="X19" t="n">
         <v>3</v>
       </c>
+      <c r="Y19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2026,6 +2086,9 @@
         <v>4</v>
       </c>
       <c r="X20" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2098,6 +2161,9 @@
       </c>
       <c r="X21" s="3" t="n">
         <v>61</v>
+      </c>
+      <c r="Y21" s="3" t="n">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -462,6 +462,7 @@
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -590,6 +591,11 @@
           <t>12.07 11:22</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>12.07 15:42</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -669,6 +675,9 @@
       <c r="Y2" t="n">
         <v>5</v>
       </c>
+      <c r="Z2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -748,6 +757,9 @@
       <c r="Y3" t="n">
         <v>2</v>
       </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -827,6 +839,9 @@
       <c r="Y4" t="n">
         <v>4</v>
       </c>
+      <c r="Z4" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -906,6 +921,9 @@
       <c r="Y5" t="n">
         <v>1</v>
       </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -985,6 +1003,9 @@
       <c r="Y6" t="n">
         <v>3</v>
       </c>
+      <c r="Z6" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1064,6 +1085,9 @@
       <c r="Y7" t="n">
         <v>1</v>
       </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1143,6 +1167,9 @@
       <c r="Y8" t="n">
         <v>2</v>
       </c>
+      <c r="Z8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1222,6 +1249,9 @@
       <c r="Y9" t="n">
         <v>1</v>
       </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1301,6 +1331,9 @@
       <c r="Y10" t="n">
         <v>2</v>
       </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1380,6 +1413,9 @@
       <c r="Y11" t="n">
         <v>6</v>
       </c>
+      <c r="Z11" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1459,6 +1495,9 @@
       <c r="Y12" t="n">
         <v>1</v>
       </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1538,6 +1577,9 @@
       <c r="Y13" t="n">
         <v>3</v>
       </c>
+      <c r="Z13" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1617,6 +1659,9 @@
       <c r="Y14" t="n">
         <v>4</v>
       </c>
+      <c r="Z14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1696,6 +1741,9 @@
       <c r="Y15" t="n">
         <v>6</v>
       </c>
+      <c r="Z15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1775,6 +1823,9 @@
       <c r="Y16" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="Z16" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1854,6 +1905,9 @@
       <c r="Y17" t="n">
         <v>9</v>
       </c>
+      <c r="Z17" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1933,6 +1987,9 @@
       <c r="Y18" t="n">
         <v>2</v>
       </c>
+      <c r="Z18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2012,6 +2069,9 @@
       <c r="Y19" t="n">
         <v>3</v>
       </c>
+      <c r="Z19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2089,6 +2149,9 @@
         <v>4</v>
       </c>
       <c r="Y20" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2164,6 +2227,9 @@
       </c>
       <c r="Y21" s="3" t="n">
         <v>62</v>
+      </c>
+      <c r="Z21" s="3" t="n">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:AA21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -463,6 +463,7 @@
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -596,6 +597,11 @@
           <t>12.07 15:42</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>12.07 19:33</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -678,6 +684,9 @@
       <c r="Z2" t="n">
         <v>5</v>
       </c>
+      <c r="AA2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -760,6 +769,9 @@
       <c r="Z3" t="n">
         <v>2</v>
       </c>
+      <c r="AA3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -842,6 +854,9 @@
       <c r="Z4" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="AA4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -924,6 +939,9 @@
       <c r="Z5" t="n">
         <v>1</v>
       </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1006,6 +1024,9 @@
       <c r="Z6" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="AA6" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1088,6 +1109,9 @@
       <c r="Z7" t="n">
         <v>1</v>
       </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1170,6 +1194,9 @@
       <c r="Z8" t="n">
         <v>2</v>
       </c>
+      <c r="AA8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1252,6 +1279,9 @@
       <c r="Z9" t="n">
         <v>1</v>
       </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1334,6 +1364,9 @@
       <c r="Z10" t="n">
         <v>2</v>
       </c>
+      <c r="AA10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1416,6 +1449,9 @@
       <c r="Z11" t="n">
         <v>6</v>
       </c>
+      <c r="AA11" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1498,6 +1534,9 @@
       <c r="Z12" t="n">
         <v>1</v>
       </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1580,6 +1619,9 @@
       <c r="Z13" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="AA13" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1662,6 +1704,9 @@
       <c r="Z14" t="n">
         <v>4</v>
       </c>
+      <c r="AA14" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1744,6 +1789,9 @@
       <c r="Z15" t="n">
         <v>6</v>
       </c>
+      <c r="AA15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1826,6 +1874,9 @@
       <c r="Z16" t="n">
         <v>3</v>
       </c>
+      <c r="AA16" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1908,6 +1959,9 @@
       <c r="Z17" t="n">
         <v>9</v>
       </c>
+      <c r="AA17" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1990,6 +2044,9 @@
       <c r="Z18" t="n">
         <v>2</v>
       </c>
+      <c r="AA18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2072,6 +2129,9 @@
       <c r="Z19" t="n">
         <v>3</v>
       </c>
+      <c r="AA19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2152,6 +2212,9 @@
         <v>4</v>
       </c>
       <c r="Z20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2230,6 +2293,9 @@
       </c>
       <c r="Z21" s="3" t="n">
         <v>65</v>
+      </c>
+      <c r="AA21" s="3" t="n">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA21"/>
+  <dimension ref="A1:AB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -464,6 +464,7 @@
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -602,6 +603,11 @@
           <t>12.07 19:33</t>
         </is>
       </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>12.07 19:39</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -687,6 +693,9 @@
       <c r="AA2" t="n">
         <v>5</v>
       </c>
+      <c r="AB2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -772,6 +781,9 @@
       <c r="AA3" t="n">
         <v>2</v>
       </c>
+      <c r="AB3" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -857,6 +869,9 @@
       <c r="AA4" t="n">
         <v>5</v>
       </c>
+      <c r="AB4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -942,6 +957,9 @@
       <c r="AA5" t="n">
         <v>1</v>
       </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1027,6 +1045,9 @@
       <c r="AA6" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="AB6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1112,6 +1133,9 @@
       <c r="AA7" t="n">
         <v>1</v>
       </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1197,6 +1221,9 @@
       <c r="AA8" t="n">
         <v>2</v>
       </c>
+      <c r="AB8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1282,6 +1309,9 @@
       <c r="AA9" t="n">
         <v>1</v>
       </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1367,6 +1397,9 @@
       <c r="AA10" t="n">
         <v>2</v>
       </c>
+      <c r="AB10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1452,6 +1485,9 @@
       <c r="AA11" t="n">
         <v>6</v>
       </c>
+      <c r="AB11" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1537,6 +1573,9 @@
       <c r="AA12" t="n">
         <v>1</v>
       </c>
+      <c r="AB12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1622,6 +1661,9 @@
       <c r="AA13" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="AB13" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1707,6 +1749,9 @@
       <c r="AA14" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="AB14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1792,6 +1837,9 @@
       <c r="AA15" t="n">
         <v>6</v>
       </c>
+      <c r="AB15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1877,6 +1925,9 @@
       <c r="AA16" t="n">
         <v>3</v>
       </c>
+      <c r="AB16" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1962,6 +2013,9 @@
       <c r="AA17" t="n">
         <v>9</v>
       </c>
+      <c r="AB17" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2047,6 +2101,9 @@
       <c r="AA18" t="n">
         <v>2</v>
       </c>
+      <c r="AB18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2132,6 +2189,9 @@
       <c r="AA19" t="n">
         <v>3</v>
       </c>
+      <c r="AB19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2215,6 +2275,9 @@
         <v>4</v>
       </c>
       <c r="AA20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2296,6 +2359,9 @@
       </c>
       <c r="AA21" s="3" t="n">
         <v>68</v>
+      </c>
+      <c r="AB21" s="3" t="n">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB21"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -465,6 +465,7 @@
     <col width="13" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -608,6 +609,11 @@
           <t>12.07 19:39</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>12.07 23:24</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -696,6 +702,9 @@
       <c r="AB2" t="n">
         <v>5</v>
       </c>
+      <c r="AC2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -784,6 +793,9 @@
       <c r="AB3" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="AC3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -872,6 +884,9 @@
       <c r="AB4" t="n">
         <v>5</v>
       </c>
+      <c r="AC4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -960,6 +975,9 @@
       <c r="AB5" t="n">
         <v>1</v>
       </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1048,6 +1066,9 @@
       <c r="AB6" t="n">
         <v>5</v>
       </c>
+      <c r="AC6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1136,6 +1157,9 @@
       <c r="AB7" t="n">
         <v>1</v>
       </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1224,6 +1248,9 @@
       <c r="AB8" t="n">
         <v>2</v>
       </c>
+      <c r="AC8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1312,6 +1339,9 @@
       <c r="AB9" t="n">
         <v>1</v>
       </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1400,6 +1430,9 @@
       <c r="AB10" t="n">
         <v>2</v>
       </c>
+      <c r="AC10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1488,6 +1521,9 @@
       <c r="AB11" t="n">
         <v>6</v>
       </c>
+      <c r="AC11" s="1" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1576,6 +1612,9 @@
       <c r="AB12" t="n">
         <v>1</v>
       </c>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1664,6 +1703,9 @@
       <c r="AB13" t="n">
         <v>5</v>
       </c>
+      <c r="AC13" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1752,6 +1794,9 @@
       <c r="AB14" t="n">
         <v>5</v>
       </c>
+      <c r="AC14" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1840,6 +1885,9 @@
       <c r="AB15" t="n">
         <v>6</v>
       </c>
+      <c r="AC15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1928,6 +1976,9 @@
       <c r="AB16" t="n">
         <v>3</v>
       </c>
+      <c r="AC16" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2016,6 +2067,9 @@
       <c r="AB17" t="n">
         <v>9</v>
       </c>
+      <c r="AC17" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2104,6 +2158,9 @@
       <c r="AB18" t="n">
         <v>2</v>
       </c>
+      <c r="AC18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2192,6 +2249,9 @@
       <c r="AB19" t="n">
         <v>3</v>
       </c>
+      <c r="AC19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2279,6 +2339,9 @@
       </c>
       <c r="AB20" t="n">
         <v>4</v>
+      </c>
+      <c r="AC20" s="1" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -2362,6 +2425,9 @@
       </c>
       <c r="AB21" s="3" t="n">
         <v>69</v>
+      </c>
+      <c r="AC21" s="3" t="n">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -466,6 +466,7 @@
     <col width="13" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -614,6 +615,11 @@
           <t>12.07 23:24</t>
         </is>
       </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>13.07 01:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -705,6 +711,9 @@
       <c r="AC2" t="n">
         <v>5</v>
       </c>
+      <c r="AD2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -796,6 +805,9 @@
       <c r="AC3" t="n">
         <v>3</v>
       </c>
+      <c r="AD3" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -887,6 +899,9 @@
       <c r="AC4" t="n">
         <v>5</v>
       </c>
+      <c r="AD4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -978,6 +993,9 @@
       <c r="AC5" t="n">
         <v>1</v>
       </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1069,6 +1087,9 @@
       <c r="AC6" t="n">
         <v>5</v>
       </c>
+      <c r="AD6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1160,6 +1181,9 @@
       <c r="AC7" t="n">
         <v>1</v>
       </c>
+      <c r="AD7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1251,6 +1275,9 @@
       <c r="AC8" t="n">
         <v>2</v>
       </c>
+      <c r="AD8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1342,6 +1369,9 @@
       <c r="AC9" t="n">
         <v>1</v>
       </c>
+      <c r="AD9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1433,6 +1463,9 @@
       <c r="AC10" t="n">
         <v>2</v>
       </c>
+      <c r="AD10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1524,6 +1557,9 @@
       <c r="AC11" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="AD11" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1615,6 +1651,9 @@
       <c r="AC12" t="n">
         <v>1</v>
       </c>
+      <c r="AD12" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1706,6 +1745,9 @@
       <c r="AC13" t="n">
         <v>5</v>
       </c>
+      <c r="AD13" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1797,6 +1839,9 @@
       <c r="AC14" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="AD14" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1888,6 +1933,9 @@
       <c r="AC15" t="n">
         <v>6</v>
       </c>
+      <c r="AD15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1979,6 +2027,9 @@
       <c r="AC16" t="n">
         <v>3</v>
       </c>
+      <c r="AD16" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2070,6 +2121,9 @@
       <c r="AC17" t="n">
         <v>9</v>
       </c>
+      <c r="AD17" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2161,6 +2215,9 @@
       <c r="AC18" t="n">
         <v>2</v>
       </c>
+      <c r="AD18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2252,6 +2309,9 @@
       <c r="AC19" t="n">
         <v>3</v>
       </c>
+      <c r="AD19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2341,6 +2401,9 @@
         <v>4</v>
       </c>
       <c r="AC20" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD20" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2428,6 +2491,9 @@
       </c>
       <c r="AC21" s="3" t="n">
         <v>73</v>
+      </c>
+      <c r="AD21" s="3" t="n">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AE21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -467,6 +467,7 @@
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="29" max="29"/>
     <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -620,6 +621,11 @@
           <t>13.07 01:00</t>
         </is>
       </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>13.07 07:47</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -714,6 +720,9 @@
       <c r="AD2" t="n">
         <v>5</v>
       </c>
+      <c r="AE2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -808,6 +817,9 @@
       <c r="AD3" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="AE3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -902,6 +914,9 @@
       <c r="AD4" t="n">
         <v>5</v>
       </c>
+      <c r="AE4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -996,6 +1011,9 @@
       <c r="AD5" t="n">
         <v>1</v>
       </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1090,6 +1108,9 @@
       <c r="AD6" t="n">
         <v>5</v>
       </c>
+      <c r="AE6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1184,6 +1205,9 @@
       <c r="AD7" t="n">
         <v>1</v>
       </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1278,6 +1302,9 @@
       <c r="AD8" t="n">
         <v>2</v>
       </c>
+      <c r="AE8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1372,6 +1399,9 @@
       <c r="AD9" t="n">
         <v>1</v>
       </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1466,6 +1496,9 @@
       <c r="AD10" t="n">
         <v>2</v>
       </c>
+      <c r="AE10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1560,6 +1593,9 @@
       <c r="AD11" t="n">
         <v>8</v>
       </c>
+      <c r="AE11" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1654,6 +1690,9 @@
       <c r="AD12" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="AE12" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1748,6 +1787,9 @@
       <c r="AD13" t="n">
         <v>5</v>
       </c>
+      <c r="AE13" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1842,6 +1884,9 @@
       <c r="AD14" t="n">
         <v>6</v>
       </c>
+      <c r="AE14" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1936,6 +1981,9 @@
       <c r="AD15" t="n">
         <v>6</v>
       </c>
+      <c r="AE15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2030,6 +2078,9 @@
       <c r="AD16" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="AE16" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2124,6 +2175,9 @@
       <c r="AD17" t="n">
         <v>9</v>
       </c>
+      <c r="AE17" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2218,6 +2272,9 @@
       <c r="AD18" t="n">
         <v>2</v>
       </c>
+      <c r="AE18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2312,6 +2369,9 @@
       <c r="AD19" t="n">
         <v>3</v>
       </c>
+      <c r="AE19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2405,6 +2465,9 @@
       </c>
       <c r="AD20" t="n">
         <v>5</v>
+      </c>
+      <c r="AE20" s="2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -2494,6 +2557,9 @@
       </c>
       <c r="AD21" s="3" t="n">
         <v>76</v>
+      </c>
+      <c r="AE21" s="3" t="n">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE21"/>
+  <dimension ref="A1:AF21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -468,6 +468,7 @@
     <col width="13" customWidth="1" min="29" max="29"/>
     <col width="13" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -626,6 +627,11 @@
           <t>13.07 07:47</t>
         </is>
       </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>13.07 10:20</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -723,6 +729,9 @@
       <c r="AE2" t="n">
         <v>5</v>
       </c>
+      <c r="AF2" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -820,6 +829,9 @@
       <c r="AE3" t="n">
         <v>4</v>
       </c>
+      <c r="AF3" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -917,6 +929,9 @@
       <c r="AE4" t="n">
         <v>5</v>
       </c>
+      <c r="AF4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1014,6 +1029,9 @@
       <c r="AE5" t="n">
         <v>1</v>
       </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1111,6 +1129,9 @@
       <c r="AE6" t="n">
         <v>5</v>
       </c>
+      <c r="AF6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1208,6 +1229,9 @@
       <c r="AE7" t="n">
         <v>1</v>
       </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1305,6 +1329,9 @@
       <c r="AE8" t="n">
         <v>2</v>
       </c>
+      <c r="AF8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1402,6 +1429,9 @@
       <c r="AE9" t="n">
         <v>1</v>
       </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1499,6 +1529,9 @@
       <c r="AE10" t="n">
         <v>2</v>
       </c>
+      <c r="AF10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1596,6 +1629,9 @@
       <c r="AE11" t="n">
         <v>8</v>
       </c>
+      <c r="AF11" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1693,6 +1729,9 @@
       <c r="AE12" t="n">
         <v>2</v>
       </c>
+      <c r="AF12" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1790,6 +1829,9 @@
       <c r="AE13" t="n">
         <v>5</v>
       </c>
+      <c r="AF13" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1887,6 +1929,9 @@
       <c r="AE14" t="n">
         <v>6</v>
       </c>
+      <c r="AF14" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1984,6 +2029,9 @@
       <c r="AE15" t="n">
         <v>6</v>
       </c>
+      <c r="AF15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2081,6 +2129,9 @@
       <c r="AE16" t="n">
         <v>4</v>
       </c>
+      <c r="AF16" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2178,6 +2229,9 @@
       <c r="AE17" t="n">
         <v>9</v>
       </c>
+      <c r="AF17" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2275,6 +2329,9 @@
       <c r="AE18" t="n">
         <v>2</v>
       </c>
+      <c r="AF18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2372,6 +2429,9 @@
       <c r="AE19" t="n">
         <v>3</v>
       </c>
+      <c r="AF19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2467,6 +2527,9 @@
         <v>5</v>
       </c>
       <c r="AE20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF20" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2560,6 +2623,9 @@
       </c>
       <c r="AE21" s="3" t="n">
         <v>77</v>
+      </c>
+      <c r="AF21" s="3" t="n">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF21"/>
+  <dimension ref="A1:AG21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -469,6 +469,7 @@
     <col width="13" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="13" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -632,6 +633,11 @@
           <t>13.07 10:20</t>
         </is>
       </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>13.07 12:36</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -732,6 +738,9 @@
       <c r="AF2" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="AG2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -832,6 +841,9 @@
       <c r="AF3" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="AG3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -932,6 +944,9 @@
       <c r="AF4" t="n">
         <v>5</v>
       </c>
+      <c r="AG4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1032,6 +1047,9 @@
       <c r="AF5" t="n">
         <v>1</v>
       </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1132,6 +1150,9 @@
       <c r="AF6" t="n">
         <v>5</v>
       </c>
+      <c r="AG6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1232,6 +1253,9 @@
       <c r="AF7" t="n">
         <v>1</v>
       </c>
+      <c r="AG7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1332,6 +1356,9 @@
       <c r="AF8" t="n">
         <v>2</v>
       </c>
+      <c r="AG8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1432,6 +1459,9 @@
       <c r="AF9" t="n">
         <v>1</v>
       </c>
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1532,6 +1562,9 @@
       <c r="AF10" t="n">
         <v>2</v>
       </c>
+      <c r="AG10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1632,6 +1665,9 @@
       <c r="AF11" t="n">
         <v>8</v>
       </c>
+      <c r="AG11" s="1" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1732,6 +1768,9 @@
       <c r="AF12" t="n">
         <v>2</v>
       </c>
+      <c r="AG12" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1832,6 +1871,9 @@
       <c r="AF13" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="AG13" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1932,6 +1974,9 @@
       <c r="AF14" t="n">
         <v>6</v>
       </c>
+      <c r="AG14" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2032,6 +2077,9 @@
       <c r="AF15" t="n">
         <v>6</v>
       </c>
+      <c r="AG15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2132,6 +2180,9 @@
       <c r="AF16" t="n">
         <v>4</v>
       </c>
+      <c r="AG16" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2232,6 +2283,9 @@
       <c r="AF17" t="n">
         <v>9</v>
       </c>
+      <c r="AG17" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2332,6 +2386,9 @@
       <c r="AF18" t="n">
         <v>2</v>
       </c>
+      <c r="AG18" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2432,6 +2489,9 @@
       <c r="AF19" t="n">
         <v>3</v>
       </c>
+      <c r="AG19" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2530,6 +2590,9 @@
         <v>6</v>
       </c>
       <c r="AF20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG20" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2626,6 +2689,9 @@
       </c>
       <c r="AF21" s="3" t="n">
         <v>80</v>
+      </c>
+      <c r="AG21" s="3" t="n">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG21"/>
+  <dimension ref="A1:AH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -470,6 +470,7 @@
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="13" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -638,6 +639,11 @@
           <t>13.07 12:36</t>
         </is>
       </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>13.07 12:47</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -741,6 +747,9 @@
       <c r="AG2" t="n">
         <v>6</v>
       </c>
+      <c r="AH2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -844,6 +853,9 @@
       <c r="AG3" t="n">
         <v>5</v>
       </c>
+      <c r="AH3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -947,6 +959,9 @@
       <c r="AG4" t="n">
         <v>5</v>
       </c>
+      <c r="AH4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1050,6 +1065,9 @@
       <c r="AG5" t="n">
         <v>1</v>
       </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1153,6 +1171,9 @@
       <c r="AG6" t="n">
         <v>5</v>
       </c>
+      <c r="AH6" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1256,6 +1277,9 @@
       <c r="AG7" t="n">
         <v>1</v>
       </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1359,6 +1383,9 @@
       <c r="AG8" t="n">
         <v>2</v>
       </c>
+      <c r="AH8" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1462,6 +1489,9 @@
       <c r="AG9" t="n">
         <v>1</v>
       </c>
+      <c r="AH9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1565,6 +1595,9 @@
       <c r="AG10" t="n">
         <v>2</v>
       </c>
+      <c r="AH10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1668,6 +1701,9 @@
       <c r="AG11" s="1" t="n">
         <v>9</v>
       </c>
+      <c r="AH11" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1771,6 +1807,9 @@
       <c r="AG12" t="n">
         <v>2</v>
       </c>
+      <c r="AH12" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1874,6 +1913,9 @@
       <c r="AG13" t="n">
         <v>6</v>
       </c>
+      <c r="AH13" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1977,6 +2019,9 @@
       <c r="AG14" t="n">
         <v>6</v>
       </c>
+      <c r="AH14" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2080,6 +2125,9 @@
       <c r="AG15" t="n">
         <v>6</v>
       </c>
+      <c r="AH15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2183,6 +2231,9 @@
       <c r="AG16" t="n">
         <v>4</v>
       </c>
+      <c r="AH16" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2286,6 +2337,9 @@
       <c r="AG17" t="n">
         <v>9</v>
       </c>
+      <c r="AH17" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2389,6 +2443,9 @@
       <c r="AG18" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="AH18" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2492,6 +2549,9 @@
       <c r="AG19" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="AH19" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2593,6 +2653,9 @@
         <v>6</v>
       </c>
       <c r="AG20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH20" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2692,6 +2755,9 @@
       </c>
       <c r="AG21" s="3" t="n">
         <v>83</v>
+      </c>
+      <c r="AH21" s="3" t="n">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH21"/>
+  <dimension ref="A1:AI21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -471,6 +471,7 @@
     <col width="13" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
     <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -644,6 +645,11 @@
           <t>13.07 12:47</t>
         </is>
       </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>13.07 13:03</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -750,6 +756,9 @@
       <c r="AH2" t="n">
         <v>6</v>
       </c>
+      <c r="AI2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -856,6 +865,9 @@
       <c r="AH3" t="n">
         <v>5</v>
       </c>
+      <c r="AI3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -962,6 +974,9 @@
       <c r="AH4" t="n">
         <v>5</v>
       </c>
+      <c r="AI4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1068,6 +1083,9 @@
       <c r="AH5" t="n">
         <v>1</v>
       </c>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1174,6 +1192,9 @@
       <c r="AH6" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="AI6" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1280,6 +1301,9 @@
       <c r="AH7" t="n">
         <v>1</v>
       </c>
+      <c r="AI7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1386,6 +1410,9 @@
       <c r="AH8" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="AI8" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1492,6 +1519,9 @@
       <c r="AH9" t="n">
         <v>1</v>
       </c>
+      <c r="AI9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1598,6 +1628,9 @@
       <c r="AH10" t="n">
         <v>2</v>
       </c>
+      <c r="AI10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1704,6 +1737,9 @@
       <c r="AH11" t="n">
         <v>9</v>
       </c>
+      <c r="AI11" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1810,6 +1846,9 @@
       <c r="AH12" t="n">
         <v>2</v>
       </c>
+      <c r="AI12" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1916,6 +1955,9 @@
       <c r="AH13" t="n">
         <v>6</v>
       </c>
+      <c r="AI13" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2022,6 +2064,9 @@
       <c r="AH14" t="n">
         <v>6</v>
       </c>
+      <c r="AI14" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2128,6 +2173,9 @@
       <c r="AH15" t="n">
         <v>6</v>
       </c>
+      <c r="AI15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2234,6 +2282,9 @@
       <c r="AH16" t="n">
         <v>4</v>
       </c>
+      <c r="AI16" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2340,6 +2391,9 @@
       <c r="AH17" t="n">
         <v>9</v>
       </c>
+      <c r="AI17" s="2" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2446,6 +2500,9 @@
       <c r="AH18" t="n">
         <v>3</v>
       </c>
+      <c r="AI18" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2552,6 +2609,9 @@
       <c r="AH19" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="AI19" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2656,6 +2716,9 @@
         <v>6</v>
       </c>
       <c r="AH20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI20" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2758,6 +2821,9 @@
       </c>
       <c r="AH21" s="3" t="n">
         <v>86</v>
+      </c>
+      <c r="AI21" s="3" t="n">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI21"/>
+  <dimension ref="A1:AJ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -472,6 +472,7 @@
     <col width="13" customWidth="1" min="33" max="33"/>
     <col width="13" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -650,6 +651,11 @@
           <t>13.07 13:03</t>
         </is>
       </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>13.07 15:32</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -759,6 +765,9 @@
       <c r="AI2" t="n">
         <v>6</v>
       </c>
+      <c r="AJ2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -868,6 +877,9 @@
       <c r="AI3" t="n">
         <v>5</v>
       </c>
+      <c r="AJ3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -977,6 +989,9 @@
       <c r="AI4" t="n">
         <v>5</v>
       </c>
+      <c r="AJ4" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1086,6 +1101,9 @@
       <c r="AI5" t="n">
         <v>1</v>
       </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1195,6 +1213,9 @@
       <c r="AI6" t="n">
         <v>6</v>
       </c>
+      <c r="AJ6" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1304,6 +1325,9 @@
       <c r="AI7" t="n">
         <v>1</v>
       </c>
+      <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1413,6 +1437,9 @@
       <c r="AI8" t="n">
         <v>3</v>
       </c>
+      <c r="AJ8" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1522,6 +1549,9 @@
       <c r="AI9" t="n">
         <v>1</v>
       </c>
+      <c r="AJ9" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1631,6 +1661,9 @@
       <c r="AI10" t="n">
         <v>2</v>
       </c>
+      <c r="AJ10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1740,6 +1773,9 @@
       <c r="AI11" t="n">
         <v>9</v>
       </c>
+      <c r="AJ11" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1849,6 +1885,9 @@
       <c r="AI12" t="n">
         <v>2</v>
       </c>
+      <c r="AJ12" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1958,6 +1997,9 @@
       <c r="AI13" t="n">
         <v>6</v>
       </c>
+      <c r="AJ13" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2067,6 +2109,9 @@
       <c r="AI14" t="n">
         <v>6</v>
       </c>
+      <c r="AJ14" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2176,6 +2221,9 @@
       <c r="AI15" t="n">
         <v>6</v>
       </c>
+      <c r="AJ15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2285,6 +2333,9 @@
       <c r="AI16" t="n">
         <v>4</v>
       </c>
+      <c r="AJ16" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2394,6 +2445,9 @@
       <c r="AI17" s="2" t="n">
         <v>10</v>
       </c>
+      <c r="AJ17" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2503,6 +2557,9 @@
       <c r="AI18" t="n">
         <v>3</v>
       </c>
+      <c r="AJ18" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2612,6 +2669,9 @@
       <c r="AI19" t="n">
         <v>5</v>
       </c>
+      <c r="AJ19" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2719,6 +2779,9 @@
         <v>6</v>
       </c>
       <c r="AI20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2824,6 +2887,9 @@
       </c>
       <c r="AI21" s="3" t="n">
         <v>87</v>
+      </c>
+      <c r="AJ21" s="3" t="n">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/output_highlighted.xlsx
+++ b/output_highlighted.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ21"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -473,6 +473,7 @@
     <col width="13" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -656,6 +657,11 @@
           <t>13.07 15:32</t>
         </is>
       </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>13.07 16:18</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -768,6 +774,9 @@
       <c r="AJ2" t="n">
         <v>6</v>
       </c>
+      <c r="AK2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -880,6 +889,9 @@
       <c r="AJ3" t="n">
         <v>5</v>
       </c>
+      <c r="AK3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -992,6 +1004,9 @@
       <c r="AJ4" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="AK4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1104,6 +1119,9 @@
       <c r="AJ5" t="n">
         <v>1</v>
       </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1216,6 +1234,9 @@
       <c r="AJ6" t="n">
         <v>6</v>
       </c>
+      <c r="AK6" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1328,6 +1349,9 @@
       <c r="AJ7" t="n">
         <v>1</v>
       </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1440,6 +1464,9 @@
       <c r="AJ8" t="n">
         <v>3</v>
       </c>
+      <c r="AK8" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1552,6 +1579,9 @@
       <c r="AJ9" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="AK9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1664,6 +1694,9 @@
       <c r="AJ10" t="n">
         <v>2</v>
       </c>
+      <c r="AK10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1776,6 +1809,9 @@
       <c r="AJ11" t="n">
         <v>9</v>
       </c>
+      <c r="AK11" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1888,6 +1924,9 @@
       <c r="AJ12" t="n">
         <v>2</v>
       </c>
+      <c r="AK12" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2000,6 +2039,9 @@
       <c r="AJ13" t="n">
         <v>6</v>
       </c>
+      <c r="AK13" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2112,6 +2154,9 @@
       <c r="AJ14" t="n">
         <v>6</v>
       </c>
+      <c r="AK14" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2224,6 +2269,9 @@
       <c r="AJ15" t="n">
         <v>6</v>
       </c>
+      <c r="AK15" s="1" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2336,6 +2384,9 @@
       <c r="AJ16" t="n">
         <v>4</v>
       </c>
+      <c r="AK16" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2448,6 +2499,9 @@
       <c r="AJ17" t="n">
         <v>10</v>
       </c>
+      <c r="AK17" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2560,6 +2614,9 @@
       <c r="AJ18" t="n">
         <v>3</v>
       </c>
+      <c r="AK18" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2672,6 +2729,9 @@
       <c r="AJ19" t="n">
         <v>5</v>
       </c>
+      <c r="AK19" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2783,6 +2843,9 @@
       </c>
       <c r="AJ20" t="n">
         <v>6</v>
+      </c>
+      <c r="AK20" s="1" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -2890,6 +2953,9 @@
       </c>
       <c r="AJ21" s="3" t="n">
         <v>89</v>
+      </c>
+      <c r="AK21" s="3" t="n">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
